--- a/business_surveys/021_livestock_feed_optimization_survey--business_surveys.xlsx
+++ b/business_surveys/021_livestock_feed_optimization_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -713,7 +713,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Feed Nutrient Balance Other</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -759,7 +759,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Feed Frequency Other</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -805,7 +805,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Feed Amount Other</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -851,7 +851,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Feed Nutrition Other</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -897,7 +897,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Feed Nutrition Frequency Other</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -943,7 +943,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Feed Frequency Of Nutrition Other</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -989,7 +989,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Nutrition Other</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Farm Location Other</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
